--- a/construction_template/data/templates_blank/daily_log_2.xlsx
+++ b/construction_template/data/templates_blank/daily_log_2.xlsx
@@ -5,7 +5,6 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EmsSuperAllSrc\EmsSupervision\xlt\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{23428746-04B4-4B97-AED4-06B7D19BD9EF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -33,16 +32,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="506">
   <si>
-    <t>任泰技術顧問有限公司</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t>公共工程監造日報表</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>第二聯</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="12"/>
         <rFont val="Times New Roman"/>
@@ -50,7 +49,7 @@
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="12"/>
         <rFont val="標楷體"/>
@@ -59,13 +58,13 @@
       </rPr>
       <t>完成工程詳細表</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="2" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>填報日期：</t>
   </si>
   <si>
-    <t>工程名稱：111年度西區水利建造物檢修改善及災後淤土、樹木復原及設施搶修預約維護工程</t>
+    <t xml:space="preserve">工程名稱：</t>
   </si>
   <si>
     <t xml:space="preserve">工  程  項  目</t>

--- a/construction_template/data/templates_blank/daily_log_2.xlsx
+++ b/construction_template/data/templates_blank/daily_log_2.xlsx
@@ -5,6 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url=""/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{23428746-04B4-4B97-AED4-06B7D19BD9EF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -32,16 +33,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="506">
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t>公共工程監造日報表</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>第二聯</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="12"/>
         <rFont val="Times New Roman"/>
@@ -49,7 +50,7 @@
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="12"/>
         <rFont val="標楷體"/>
@@ -58,13 +59,13 @@
       </rPr>
       <t>完成工程詳細表</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>填報日期：</t>
   </si>
   <si>
-    <t xml:space="preserve">工程名稱：</t>
+    <t>工程名稱：</t>
   </si>
   <si>
     <t xml:space="preserve">工  程  項  目</t>
@@ -2068,7 +2069,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F463"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
